--- a/Results_experiment/exp_5/preds_1111114442222222.xlsx
+++ b/Results_experiment/exp_5/preds_1111114442222222.xlsx
@@ -1179,7 +1179,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D2">
-        <v>1.859658479690552</v>
+        <v>1.865266561508179</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D3">
-        <v>4.396048545837402</v>
+        <v>2.228168725967407</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1207,7 +1207,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D4">
-        <v>2.601120471954346</v>
+        <v>1.803094863891602</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1221,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>1.688744783401489</v>
+        <v>1.867625713348389</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D6">
-        <v>3.406849384307861</v>
+        <v>4.675721645355225</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1249,7 +1249,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>4.627228736877441</v>
+        <v>4.560999870300293</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>3.03937840461731</v>
+        <v>1.88812255859375</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D9">
-        <v>8.70807933807373</v>
+        <v>8.285758972167969</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D10">
-        <v>7.345864295959473</v>
+        <v>6.25419282913208</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1305,7 +1305,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D11">
-        <v>2.063366889953613</v>
+        <v>1.930719375610352</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1319,7 +1319,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D12">
-        <v>1.798270702362061</v>
+        <v>1.885524034500122</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1333,7 +1333,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D13">
-        <v>9.212701797485352</v>
+        <v>9.539004325866699</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1347,7 +1347,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D14">
-        <v>2.311805963516235</v>
+        <v>2.746996641159058</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1361,7 +1361,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D15">
-        <v>1.666043996810913</v>
+        <v>1.741914987564087</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1375,7 +1375,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D16">
-        <v>1.824930429458618</v>
+        <v>2.158014535903931</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1389,7 +1389,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D17">
-        <v>1.782160997390747</v>
+        <v>1.774407863616943</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1403,7 +1403,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D18">
-        <v>9.842179298400879</v>
+        <v>9.180685043334961</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1417,7 +1417,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D19">
-        <v>1.617066621780396</v>
+        <v>1.695514440536499</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1431,7 +1431,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D20">
-        <v>7.420879364013672</v>
+        <v>7.393640041351318</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1445,7 +1445,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D21">
-        <v>2.033713102340698</v>
+        <v>1.889079570770264</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1459,7 +1459,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D22">
-        <v>2.319672822952271</v>
+        <v>2.459230184555054</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1473,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>2.029559850692749</v>
+        <v>1.938776016235352</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1487,7 +1487,7 @@
         <v>11.5</v>
       </c>
       <c r="D24">
-        <v>3.725869655609131</v>
+        <v>3.372433185577393</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1501,7 +1501,7 @@
         <v>14.5</v>
       </c>
       <c r="D25">
-        <v>6.76871395111084</v>
+        <v>6.709563732147217</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1.64624547958374</v>
+        <v>2.692437171936035</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1529,7 +1529,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D27">
-        <v>2.008893013000488</v>
+        <v>1.866696834564209</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1543,7 +1543,7 @@
         <v>26.89999961853027</v>
       </c>
       <c r="D28">
-        <v>14.81519985198975</v>
+        <v>15.09208202362061</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1557,7 +1557,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D29">
-        <v>3.485225200653076</v>
+        <v>3.270860910415649</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1571,7 +1571,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D30">
-        <v>1.557345271110535</v>
+        <v>1.727829575538635</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1585,7 +1585,7 @@
         <v>10.5</v>
       </c>
       <c r="D31">
-        <v>2.430018901824951</v>
+        <v>2.151427984237671</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1599,7 +1599,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D32">
-        <v>2.293911933898926</v>
+        <v>2.052216053009033</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1613,7 +1613,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D33">
-        <v>6.439686298370361</v>
+        <v>7.058817863464355</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1627,7 +1627,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D34">
-        <v>2.220058917999268</v>
+        <v>3.20874547958374</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1641,7 +1641,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D35">
-        <v>2.263507843017578</v>
+        <v>2.447372436523438</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1655,7 +1655,7 @@
         <v>6.5</v>
       </c>
       <c r="D36">
-        <v>5.615950584411621</v>
+        <v>5.249068737030029</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1669,7 +1669,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D37">
-        <v>1.925793647766113</v>
+        <v>3.728826522827148</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1683,7 +1683,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D38">
-        <v>5.981989860534668</v>
+        <v>5.724662780761719</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1697,7 +1697,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D39">
-        <v>7.483846187591553</v>
+        <v>7.702356815338135</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1711,7 +1711,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D40">
-        <v>3.594738006591797</v>
+        <v>3.016531944274902</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1725,7 +1725,7 @@
         <v>1.5</v>
       </c>
       <c r="D41">
-        <v>3.309097290039062</v>
+        <v>4.372400760650635</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1739,7 +1739,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D42">
-        <v>1.765448570251465</v>
+        <v>1.815189123153687</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1753,7 +1753,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D43">
-        <v>1.831697463989258</v>
+        <v>1.969906330108643</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1767,7 +1767,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D44">
-        <v>1.641203880310059</v>
+        <v>1.76444685459137</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1781,7 +1781,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>5.055389881134033</v>
+        <v>5.301041603088379</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1795,7 +1795,7 @@
         <v>3.5</v>
       </c>
       <c r="D46">
-        <v>1.779938936233521</v>
+        <v>1.800014495849609</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1809,7 +1809,7 @@
         <v>0.5</v>
       </c>
       <c r="D47">
-        <v>2.255987167358398</v>
+        <v>2.282422065734863</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1823,7 +1823,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D48">
-        <v>1.70459771156311</v>
+        <v>1.792447328567505</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1837,7 +1837,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D49">
-        <v>2.670515775680542</v>
+        <v>2.579787015914917</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1851,7 +1851,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="D50">
-        <v>5.499565124511719</v>
+        <v>8.111775398254395</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1865,7 +1865,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>3.053712844848633</v>
+        <v>2.02497124671936</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1879,7 +1879,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D52">
-        <v>2.049746036529541</v>
+        <v>1.714541673660278</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1893,7 +1893,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D53">
-        <v>4.706456184387207</v>
+        <v>3.591032743453979</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>6.011237144470215</v>
+        <v>5.875672340393066</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D55">
-        <v>1.588402271270752</v>
+        <v>1.738597631454468</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D56">
-        <v>1.798224687576294</v>
+        <v>2.374547243118286</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D57">
-        <v>1.855793476104736</v>
+        <v>1.856955051422119</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D58">
-        <v>1.731842756271362</v>
+        <v>1.776214838027954</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>2.051181077957153</v>
+        <v>2.253450632095337</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D60">
-        <v>1.607876539230347</v>
+        <v>1.952931880950928</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="D61">
-        <v>1.730773210525513</v>
+        <v>1.875620365142822</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D62">
-        <v>7.904905319213867</v>
+        <v>6.835294246673584</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2033,7 +2033,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D63">
-        <v>1.93978476524353</v>
+        <v>1.821038961410522</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2047,7 +2047,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D64">
-        <v>1.97268533706665</v>
+        <v>1.887101650238037</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2061,7 +2061,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D65">
-        <v>2.684948921203613</v>
+        <v>2.70534086227417</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2075,7 +2075,7 @@
         <v>3.5</v>
       </c>
       <c r="D66">
-        <v>2.152392625808716</v>
+        <v>3.051314353942871</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2089,7 +2089,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D67">
-        <v>2.067041158676147</v>
+        <v>1.961189270019531</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2103,7 +2103,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D68">
-        <v>2.289584875106812</v>
+        <v>2.100240468978882</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2117,7 +2117,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>1.995105266571045</v>
+        <v>1.892834424972534</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2131,7 +2131,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D70">
-        <v>2.525251865386963</v>
+        <v>1.757234573364258</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="D71">
-        <v>2.338051319122314</v>
+        <v>2.236081600189209</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2159,7 +2159,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D72">
-        <v>3.377488613128662</v>
+        <v>3.551382064819336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2173,7 +2173,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D73">
-        <v>3.663979530334473</v>
+        <v>4.1036376953125</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2187,7 +2187,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>1.744887828826904</v>
+        <v>3.022648572921753</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2201,7 +2201,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D75">
-        <v>1.838484048843384</v>
+        <v>1.935675382614136</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2215,7 +2215,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D76">
-        <v>6.177462577819824</v>
+        <v>6.716403961181641</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2229,7 +2229,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D77">
-        <v>5.292048454284668</v>
+        <v>5.450747489929199</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2243,7 +2243,7 @@
         <v>3.5</v>
       </c>
       <c r="D78">
-        <v>1.809785127639771</v>
+        <v>1.779328346252441</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2257,7 +2257,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D79">
-        <v>1.618815898895264</v>
+        <v>1.901235818862915</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2271,7 +2271,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D80">
-        <v>2.660312652587891</v>
+        <v>3.15509295463562</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2285,7 +2285,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D81">
-        <v>5.004120826721191</v>
+        <v>6.128822803497314</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2299,7 +2299,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D82">
-        <v>4.105915069580078</v>
+        <v>4.591104030609131</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2313,7 +2313,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D83">
-        <v>2.094027757644653</v>
+        <v>2.37349271774292</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2327,7 +2327,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D84">
-        <v>2.696310758590698</v>
+        <v>2.747902631759644</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2341,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="D85">
-        <v>3.152793645858765</v>
+        <v>3.563348293304443</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2355,7 +2355,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D86">
-        <v>2.214995145797729</v>
+        <v>2.823179483413696</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2369,7 +2369,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D87">
-        <v>1.787510871887207</v>
+        <v>1.918124914169312</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2383,7 +2383,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D88">
-        <v>4.699413776397705</v>
+        <v>5.996662616729736</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2397,7 +2397,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D89">
-        <v>1.762979030609131</v>
+        <v>1.947098731994629</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2411,7 +2411,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D90">
-        <v>1.911735773086548</v>
+        <v>1.901766300201416</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2425,7 +2425,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>9.85465145111084</v>
+        <v>9.308658599853516</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2439,7 +2439,7 @@
         <v>0.5</v>
       </c>
       <c r="D92">
-        <v>3.857685089111328</v>
+        <v>4.241831302642822</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2453,7 +2453,7 @@
         <v>4</v>
       </c>
       <c r="D93">
-        <v>5.301863670349121</v>
+        <v>6.043057918548584</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2467,7 +2467,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>2.299732685089111</v>
+        <v>2.01637864112854</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2481,7 +2481,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D95">
-        <v>1.660025358200073</v>
+        <v>1.899178504943848</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2495,7 +2495,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D96">
-        <v>3.074604988098145</v>
+        <v>2.514093399047852</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2509,7 +2509,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D97">
-        <v>5.476595878601074</v>
+        <v>5.806465625762939</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2523,7 +2523,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D98">
-        <v>6.343865871429443</v>
+        <v>6.133279323577881</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2537,7 +2537,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D99">
-        <v>1.999554395675659</v>
+        <v>1.97293758392334</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2551,7 +2551,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D100">
-        <v>2.11629581451416</v>
+        <v>4.318692684173584</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2565,7 +2565,7 @@
         <v>4.5</v>
       </c>
       <c r="D101">
-        <v>3.294726848602295</v>
+        <v>2.824766159057617</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2579,7 +2579,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D102">
-        <v>1.994112014770508</v>
+        <v>2.737032651901245</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2593,7 +2593,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D103">
-        <v>1.848795413970947</v>
+        <v>1.859042644500732</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2607,7 +2607,7 @@
         <v>10.5</v>
       </c>
       <c r="D104">
-        <v>2.59528923034668</v>
+        <v>3.917436361312866</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2621,7 +2621,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D105">
-        <v>1.61615777015686</v>
+        <v>1.757706880569458</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2635,7 +2635,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D106">
-        <v>1.967143297195435</v>
+        <v>1.912526369094849</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2649,7 +2649,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D107">
-        <v>9.536015510559082</v>
+        <v>8.586770057678223</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2663,7 +2663,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D108">
-        <v>6.557860851287842</v>
+        <v>5.620723724365234</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2677,7 +2677,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D109">
-        <v>8.390379905700684</v>
+        <v>8.390517234802246</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2691,7 +2691,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D110">
-        <v>5.269003868103027</v>
+        <v>5.284168720245361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2705,7 +2705,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D111">
-        <v>7.127139568328857</v>
+        <v>7.701064586639404</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2719,7 +2719,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D112">
-        <v>2.839292526245117</v>
+        <v>1.761964082717896</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2733,7 +2733,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D113">
-        <v>2.267672300338745</v>
+        <v>2.471037626266479</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2747,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="D114">
-        <v>2.331917524337769</v>
+        <v>2.378140687942505</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2761,7 +2761,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D115">
-        <v>1.813884735107422</v>
+        <v>1.973268985748291</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2775,7 +2775,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="D116">
-        <v>14.2080192565918</v>
+        <v>16.05507850646973</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2789,7 +2789,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D117">
-        <v>1.740079641342163</v>
+        <v>2.327349901199341</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2803,7 +2803,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D118">
-        <v>3.181267261505127</v>
+        <v>2.654693365097046</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2817,7 +2817,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D119">
-        <v>2.607067346572876</v>
+        <v>3.043319940567017</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2831,7 +2831,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D120">
-        <v>3.0506591796875</v>
+        <v>3.589531183242798</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2845,7 +2845,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D121">
-        <v>1.846842050552368</v>
+        <v>2.156421661376953</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2859,7 +2859,7 @@
         <v>20.10000038146973</v>
       </c>
       <c r="D122">
-        <v>2.264945030212402</v>
+        <v>2.527618646621704</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2873,7 +2873,7 @@
         <v>6.5</v>
       </c>
       <c r="D123">
-        <v>6.814154624938965</v>
+        <v>7.604462146759033</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2887,7 +2887,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D124">
-        <v>1.799030065536499</v>
+        <v>1.797167778015137</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2901,7 +2901,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D125">
-        <v>1.662049770355225</v>
+        <v>1.821899652481079</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D126">
-        <v>1.985518932342529</v>
+        <v>1.880817651748657</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2929,7 +2929,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D127">
-        <v>3.229920864105225</v>
+        <v>3.522958040237427</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2943,7 +2943,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D128">
-        <v>1.593672752380371</v>
+        <v>2.126551628112793</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2957,7 +2957,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D129">
-        <v>3.109271287918091</v>
+        <v>2.450707912445068</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2971,7 +2971,7 @@
         <v>0.5</v>
       </c>
       <c r="D130">
-        <v>3.185705184936523</v>
+        <v>1.96967077255249</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2985,7 +2985,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D131">
-        <v>2.000853776931763</v>
+        <v>1.866494417190552</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2999,7 +2999,7 @@
         <v>2.5</v>
       </c>
       <c r="D132">
-        <v>1.916676998138428</v>
+        <v>2.02635645866394</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3013,7 +3013,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="D133">
-        <v>19.4636344909668</v>
+        <v>19.02624702453613</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3027,7 +3027,7 @@
         <v>0.5</v>
       </c>
       <c r="D134">
-        <v>1.84136176109314</v>
+        <v>1.908902645111084</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3041,7 +3041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D135">
-        <v>6.971387386322021</v>
+        <v>7.073273181915283</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3055,7 +3055,7 @@
         <v>18.70000076293945</v>
       </c>
       <c r="D136">
-        <v>10.51021671295166</v>
+        <v>10.38196086883545</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3069,7 +3069,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D137">
-        <v>1.868083238601685</v>
+        <v>2.14127516746521</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D138">
-        <v>4.983046531677246</v>
+        <v>4.760193824768066</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3097,7 +3097,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D139">
-        <v>4.114119529724121</v>
+        <v>2.752301454544067</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3111,7 +3111,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D140">
-        <v>1.836735248565674</v>
+        <v>2.032490968704224</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3125,7 +3125,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D141">
-        <v>7.315848827362061</v>
+        <v>7.493819713592529</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3139,7 +3139,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D142">
-        <v>1.756503343582153</v>
+        <v>1.80608868598938</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D143">
-        <v>5.416150093078613</v>
+        <v>4.687225341796875</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D144">
-        <v>2.897655963897705</v>
+        <v>2.061639308929443</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>2.5</v>
       </c>
       <c r="D145">
-        <v>1.919579982757568</v>
+        <v>1.917263031005859</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D146">
-        <v>7.188119888305664</v>
+        <v>7.204391002655029</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>13.5</v>
       </c>
       <c r="D147">
-        <v>9.184678077697754</v>
+        <v>9.302180290222168</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D148">
-        <v>5.089508056640625</v>
+        <v>2.090934991836548</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D149">
-        <v>2.041393995285034</v>
+        <v>2.202577114105225</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3251,7 +3251,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D150">
-        <v>8.506935119628906</v>
+        <v>8.214469909667969</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3265,7 +3265,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D151">
-        <v>3.910200119018555</v>
+        <v>4.362816333770752</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D152">
-        <v>1.820131063461304</v>
+        <v>2.039260149002075</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D153">
-        <v>5.890968322753906</v>
+        <v>6.753669738769531</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3307,7 +3307,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D154">
-        <v>1.754525899887085</v>
+        <v>1.817542314529419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3321,7 +3321,7 @@
         <v>1.5</v>
       </c>
       <c r="D155">
-        <v>1.644483089447021</v>
+        <v>1.753999948501587</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3335,7 +3335,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D156">
-        <v>3.176835536956787</v>
+        <v>2.654500246047974</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D157">
-        <v>1.758138179779053</v>
+        <v>1.865785360336304</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3363,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="D158">
-        <v>4.646011829376221</v>
+        <v>3.384289026260376</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D159">
-        <v>1.623095035552979</v>
+        <v>1.99148964881897</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="D160">
-        <v>2.338877439498901</v>
+        <v>2.52094030380249</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>8</v>
       </c>
       <c r="D161">
-        <v>9.344098091125488</v>
+        <v>9.486360549926758</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D162">
-        <v>1.582635879516602</v>
+        <v>1.70554256439209</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D163">
-        <v>3.088138580322266</v>
+        <v>3.1131591796875</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>0.5</v>
       </c>
       <c r="D164">
-        <v>2.044487953186035</v>
+        <v>1.761240482330322</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D165">
-        <v>1.729362964630127</v>
+        <v>1.85217809677124</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>4.5</v>
       </c>
       <c r="D166">
-        <v>2.100290298461914</v>
+        <v>2.325497388839722</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3489,7 +3489,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D167">
-        <v>2.781925201416016</v>
+        <v>2.039268255233765</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3503,7 +3503,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D168">
-        <v>6.418414115905762</v>
+        <v>5.963748931884766</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3517,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="D169">
-        <v>2.176164150238037</v>
+        <v>1.905128955841064</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>1.5</v>
       </c>
       <c r="D170">
-        <v>1.779087066650391</v>
+        <v>2.164515018463135</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D171">
-        <v>5.289854049682617</v>
+        <v>5.909384250640869</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D172">
-        <v>2.138567686080933</v>
+        <v>3.225826025009155</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>10.5</v>
       </c>
       <c r="D173">
-        <v>8.59321117401123</v>
+        <v>8.567888259887695</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D174">
-        <v>2.43175745010376</v>
+        <v>2.345779657363892</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D175">
-        <v>5.08172607421875</v>
+        <v>5.128525733947754</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D176">
-        <v>2.815719604492188</v>
+        <v>3.191444158554077</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3629,7 +3629,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D177">
-        <v>1.804352760314941</v>
+        <v>2.250259399414062</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D178">
-        <v>5.108176231384277</v>
+        <v>6.078728675842285</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D179">
-        <v>2.603144645690918</v>
+        <v>1.74384331703186</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>3.248888969421387</v>
+        <v>2.910945653915405</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D181">
-        <v>2.031513929367065</v>
+        <v>1.77132773399353</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="D182">
-        <v>1.836123466491699</v>
+        <v>1.807444334030151</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D183">
-        <v>4.816776275634766</v>
+        <v>4.84077787399292</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D184">
-        <v>4.239625453948975</v>
+        <v>3.18013596534729</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>3</v>
       </c>
       <c r="D185">
-        <v>2.924064159393311</v>
+        <v>2.296974182128906</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3755,7 +3755,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D186">
-        <v>1.893615007400513</v>
+        <v>2.999857664108276</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3769,7 +3769,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D187">
-        <v>7.158019542694092</v>
+        <v>6.374841690063477</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3783,7 +3783,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D188">
-        <v>1.789024353027344</v>
+        <v>1.800955295562744</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3797,7 +3797,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D189">
-        <v>2.46200704574585</v>
+        <v>2.113530397415161</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3811,7 +3811,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D190">
-        <v>1.953861951828003</v>
+        <v>1.840800046920776</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3825,7 +3825,7 @@
         <v>1.5</v>
       </c>
       <c r="D191">
-        <v>1.689210891723633</v>
+        <v>1.775483727455139</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>1.79984974861145</v>
+        <v>2.681110143661499</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D193">
-        <v>4.794972896575928</v>
+        <v>4.767693996429443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3867,7 +3867,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D194">
-        <v>8.723217964172363</v>
+        <v>8.713425636291504</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3881,7 +3881,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D195">
-        <v>5.582880020141602</v>
+        <v>5.693057537078857</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3895,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="D196">
-        <v>1.717412710189819</v>
+        <v>1.715166926383972</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3909,7 +3909,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D197">
-        <v>4.807716369628906</v>
+        <v>4.957461833953857</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3923,7 +3923,7 @@
         <v>2.5</v>
       </c>
       <c r="D198">
-        <v>1.695618152618408</v>
+        <v>1.815820455551147</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D199">
-        <v>4.758916854858398</v>
+        <v>5.898651599884033</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3951,7 +3951,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D200">
-        <v>1.915127038955688</v>
+        <v>1.804484844207764</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3965,7 +3965,7 @@
         <v>8.5</v>
       </c>
       <c r="D201">
-        <v>2.199806690216064</v>
+        <v>2.641937255859375</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3979,7 +3979,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D202">
-        <v>4.983875274658203</v>
+        <v>4.447648525238037</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3993,7 +3993,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D203">
-        <v>3.505662441253662</v>
+        <v>3.504749774932861</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4007,7 +4007,7 @@
         <v>1.5</v>
       </c>
       <c r="D204">
-        <v>1.727595806121826</v>
+        <v>2.929079294204712</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4021,7 +4021,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D205">
-        <v>10.81567478179932</v>
+        <v>10.45504283905029</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D206">
-        <v>2.393636465072632</v>
+        <v>3.64220929145813</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4049,7 +4049,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D207">
-        <v>2.56610369682312</v>
+        <v>1.920662641525269</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4063,7 +4063,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D208">
-        <v>4.175475597381592</v>
+        <v>4.246351718902588</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4077,7 +4077,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D209">
-        <v>1.700621128082275</v>
+        <v>1.966755390167236</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4091,7 +4091,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D210">
-        <v>1.759883165359497</v>
+        <v>1.843337059020996</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4105,7 +4105,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D211">
-        <v>4.637149810791016</v>
+        <v>4.653490543365479</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4119,7 +4119,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D212">
-        <v>4.313333988189697</v>
+        <v>5.896504878997803</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4133,7 +4133,7 @@
         <v>1.5</v>
       </c>
       <c r="D213">
-        <v>1.962488412857056</v>
+        <v>2.906759023666382</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4147,7 +4147,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D214">
-        <v>8.066174507141113</v>
+        <v>8.060935020446777</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4161,7 +4161,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D215">
-        <v>3.690395593643188</v>
+        <v>3.940876722335815</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D216">
-        <v>2.353434562683105</v>
+        <v>3.375719785690308</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D217">
-        <v>2.061896085739136</v>
+        <v>2.034134864807129</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D218">
-        <v>7.744229793548584</v>
+        <v>7.692455768585205</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>4.5</v>
       </c>
       <c r="D219">
-        <v>2.103661298751831</v>
+        <v>2.203614473342896</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D220">
-        <v>1.781547546386719</v>
+        <v>1.660837888717651</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D221">
-        <v>6.294927597045898</v>
+        <v>6.573785781860352</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D222">
-        <v>8.030376434326172</v>
+        <v>7.726139545440674</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D223">
-        <v>2.141963005065918</v>
+        <v>1.879999876022339</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4287,7 +4287,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D224">
-        <v>2.733477830886841</v>
+        <v>2.884645700454712</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D225">
-        <v>2.209792852401733</v>
+        <v>2.244309902191162</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4315,7 +4315,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>1.862356424331665</v>
+        <v>1.882062196731567</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="D227">
-        <v>1.97576379776001</v>
+        <v>1.913949489593506</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D228">
-        <v>2.0154709815979</v>
+        <v>1.886893272399902</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D229">
-        <v>6.878232955932617</v>
+        <v>6.636975765228271</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D230">
-        <v>2.82009220123291</v>
+        <v>2.288279056549072</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>2.485674619674683</v>
+        <v>2.103533267974854</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D232">
-        <v>7.839973449707031</v>
+        <v>7.67255163192749</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D233">
-        <v>1.953023433685303</v>
+        <v>1.891246318817139</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D234">
-        <v>2.134080648422241</v>
+        <v>2.435429096221924</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D235">
-        <v>3.07274866104126</v>
+        <v>3.591898679733276</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>4.351579189300537</v>
+        <v>4.564250469207764</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4469,7 +4469,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D237">
-        <v>1.812646150588989</v>
+        <v>1.794912457466125</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D238">
-        <v>2.031075716018677</v>
+        <v>1.818503618240356</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>3.5</v>
       </c>
       <c r="D239">
-        <v>4.017585277557373</v>
+        <v>3.984885931015015</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D240">
-        <v>1.753079175949097</v>
+        <v>2.056852579116821</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4525,7 +4525,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D241">
-        <v>2.087935924530029</v>
+        <v>2.17560863494873</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D242">
-        <v>1.842293500900269</v>
+        <v>1.998644828796387</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4553,7 +4553,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D243">
-        <v>2.252786874771118</v>
+        <v>1.940912961959839</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4567,7 +4567,7 @@
         <v>5</v>
       </c>
       <c r="D244">
-        <v>5.473162174224854</v>
+        <v>4.975080966949463</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D245">
-        <v>10.7880163192749</v>
+        <v>10.06505393981934</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4595,7 +4595,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D246">
-        <v>4.864018440246582</v>
+        <v>5.067671775817871</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D247">
-        <v>1.732469797134399</v>
+        <v>1.78079879283905</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4623,7 +4623,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D248">
-        <v>5.061665534973145</v>
+        <v>4.815663814544678</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4637,7 +4637,7 @@
         <v>6.5</v>
       </c>
       <c r="D249">
-        <v>1.708173751831055</v>
+        <v>1.843761444091797</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D250">
-        <v>2.274902105331421</v>
+        <v>1.947267532348633</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4665,7 +4665,7 @@
         <v>2.5</v>
       </c>
       <c r="D251">
-        <v>1.755566120147705</v>
+        <v>1.789259195327759</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4679,7 +4679,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>3.091793060302734</v>
+        <v>3.346898794174194</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D253">
-        <v>5.167660713195801</v>
+        <v>4.614552021026611</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>5.714834690093994</v>
+        <v>5.550874710083008</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D255">
-        <v>4.160358905792236</v>
+        <v>4.26617431640625</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D256">
-        <v>2.099090814590454</v>
+        <v>2.367027521133423</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4749,7 +4749,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D257">
-        <v>1.92710542678833</v>
+        <v>1.934839963912964</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4763,7 +4763,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>1.900497198104858</v>
+        <v>1.826862096786499</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D259">
-        <v>2.028159379959106</v>
+        <v>1.94049334526062</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D260">
-        <v>2.173839330673218</v>
+        <v>1.901747941970825</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>9.5</v>
       </c>
       <c r="D261">
-        <v>3.9040687084198</v>
+        <v>4.50469970703125</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D262">
-        <v>1.775509595870972</v>
+        <v>1.944355249404907</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4833,7 +4833,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D263">
-        <v>2.269999980926514</v>
+        <v>2.043993711471558</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D264">
-        <v>5.176374912261963</v>
+        <v>5.344688892364502</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D265">
-        <v>1.571300268173218</v>
+        <v>1.817540884017944</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D266">
-        <v>4.502315521240234</v>
+        <v>4.499230861663818</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D267">
-        <v>4.31165885925293</v>
+        <v>4.022177696228027</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D268">
-        <v>2.590949535369873</v>
+        <v>2.569622993469238</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D269">
-        <v>7.519248008728027</v>
+        <v>7.101739406585693</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D270">
-        <v>1.721429347991943</v>
+        <v>2.025322675704956</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D271">
-        <v>2.367041349411011</v>
+        <v>2.828500032424927</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D272">
-        <v>1.907444477081299</v>
+        <v>1.795443296432495</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4973,7 +4973,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D273">
-        <v>2.490017652511597</v>
+        <v>4.237636566162109</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D274">
-        <v>3.839212417602539</v>
+        <v>5.769540309906006</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>1.986072778701782</v>
+        <v>1.907221794128418</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D276">
-        <v>1.923559427261353</v>
+        <v>3.209102392196655</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5029,7 +5029,7 @@
         <v>8.5</v>
       </c>
       <c r="D277">
-        <v>6.906592845916748</v>
+        <v>7.460751056671143</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>0.5</v>
       </c>
       <c r="D278">
-        <v>6.114892959594727</v>
+        <v>6.258769512176514</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D279">
-        <v>6.444861888885498</v>
+        <v>5.604798793792725</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D280">
-        <v>2.212246179580688</v>
+        <v>1.786018371582031</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D281">
-        <v>1.757576704025269</v>
+        <v>2.019306182861328</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D282">
-        <v>1.790220499038696</v>
+        <v>1.887615919113159</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5113,7 +5113,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D283">
-        <v>2.573455095291138</v>
+        <v>2.349027872085571</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5127,7 +5127,7 @@
         <v>35.70000076293945</v>
       </c>
       <c r="D284">
-        <v>25.79230690002441</v>
+        <v>23.0638542175293</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D285">
-        <v>3.284341335296631</v>
+        <v>3.190967321395874</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D286">
-        <v>9.963625907897949</v>
+        <v>10.03149890899658</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D287">
-        <v>1.948490858078003</v>
+        <v>2.493490934371948</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>4.208817958831787</v>
+        <v>4.293224334716797</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>0.5</v>
       </c>
       <c r="D289">
-        <v>1.87814736366272</v>
+        <v>1.850229740142822</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D290">
-        <v>1.919124841690063</v>
+        <v>2.188517808914185</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>1.5</v>
       </c>
       <c r="D291">
-        <v>1.793544054031372</v>
+        <v>1.833504199981689</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>1.801494121551514</v>
+        <v>1.881327629089355</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D293">
-        <v>2.01747465133667</v>
+        <v>2.019911766052246</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5267,7 +5267,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D294">
-        <v>1.702883958816528</v>
+        <v>1.869448184967041</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5281,7 +5281,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D295">
-        <v>3.721777677536011</v>
+        <v>4.4931640625</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5295,7 +5295,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D296">
-        <v>1.705654144287109</v>
+        <v>1.838913202285767</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5309,7 +5309,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D297">
-        <v>9.814833641052246</v>
+        <v>10.3878698348999</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5323,7 +5323,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D298">
-        <v>5.245747566223145</v>
+        <v>4.501939296722412</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5337,7 +5337,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D299">
-        <v>9.292387962341309</v>
+        <v>8.534478187561035</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="D300">
-        <v>2.225649356842041</v>
+        <v>1.68231201171875</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5365,7 +5365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D301">
-        <v>9.670435905456543</v>
+        <v>9.69374942779541</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5379,7 +5379,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D302">
-        <v>1.8127760887146</v>
+        <v>1.986461639404297</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="D303">
-        <v>6.115664005279541</v>
+        <v>6.617770671844482</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5407,7 +5407,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D304">
-        <v>2.236743927001953</v>
+        <v>3.521535634994507</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5421,7 +5421,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D305">
-        <v>1.765563488006592</v>
+        <v>2.415940761566162</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D306">
-        <v>4.028176307678223</v>
+        <v>4.140652656555176</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5449,7 +5449,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D307">
-        <v>1.755873203277588</v>
+        <v>1.882455587387085</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5463,7 +5463,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D308">
-        <v>1.81374716758728</v>
+        <v>1.833822727203369</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5477,7 +5477,7 @@
         <v>1.5</v>
       </c>
       <c r="D309">
-        <v>1.917142152786255</v>
+        <v>1.891949653625488</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5491,7 +5491,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D310">
-        <v>1.644437789916992</v>
+        <v>1.712375640869141</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5505,7 +5505,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D311">
-        <v>1.641056060791016</v>
+        <v>2.396101713180542</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5519,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="D312">
-        <v>1.815927982330322</v>
+        <v>1.87913703918457</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="D313">
-        <v>4.519425868988037</v>
+        <v>4.460534572601318</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5547,7 +5547,7 @@
         <v>2.5</v>
       </c>
       <c r="D314">
-        <v>3.407473802566528</v>
+        <v>2.718674659729004</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5561,7 +5561,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D315">
-        <v>2.492111921310425</v>
+        <v>2.365009069442749</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5575,7 +5575,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D316">
-        <v>1.802926301956177</v>
+        <v>2.306685447692871</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5589,7 +5589,7 @@
         <v>7.5</v>
       </c>
       <c r="D317">
-        <v>1.994269847869873</v>
+        <v>2.186967372894287</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5603,7 +5603,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D318">
-        <v>1.745463371276855</v>
+        <v>1.979410171508789</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5617,7 +5617,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D319">
-        <v>1.75842809677124</v>
+        <v>1.903908967971802</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5631,7 +5631,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D320">
-        <v>7.921127319335938</v>
+        <v>8.181704521179199</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5645,7 +5645,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D321">
-        <v>2.947298765182495</v>
+        <v>2.603572368621826</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5659,7 +5659,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D322">
-        <v>2.094833135604858</v>
+        <v>2.327994108200073</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5673,7 +5673,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D323">
-        <v>2.358710289001465</v>
+        <v>2.283445119857788</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5687,7 +5687,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D324">
-        <v>5.575119972229004</v>
+        <v>5.299099445343018</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5701,7 +5701,7 @@
         <v>7.5</v>
       </c>
       <c r="D325">
-        <v>4.3713698387146</v>
+        <v>3.875099420547485</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5715,7 +5715,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D326">
-        <v>1.847965002059937</v>
+        <v>1.888078212738037</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5729,7 +5729,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D327">
-        <v>2.26304030418396</v>
+        <v>2.3746657371521</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5743,7 +5743,7 @@
         <v>1</v>
       </c>
       <c r="D328">
-        <v>1.727567434310913</v>
+        <v>1.854402542114258</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5757,7 +5757,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D329">
-        <v>2.190353393554688</v>
+        <v>2.45144248008728</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5771,7 +5771,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D330">
-        <v>4.949257850646973</v>
+        <v>2.299764394760132</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5785,7 +5785,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D331">
-        <v>1.808274745941162</v>
+        <v>1.968538045883179</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5799,7 +5799,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>3.298817157745361</v>
+        <v>2.19325065612793</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5813,7 +5813,7 @@
         <v>11</v>
       </c>
       <c r="D333">
-        <v>4.39261531829834</v>
+        <v>4.275389671325684</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5827,7 +5827,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D334">
-        <v>9.869270324707031</v>
+        <v>9.829645156860352</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5841,7 +5841,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D335">
-        <v>5.136150360107422</v>
+        <v>4.628776550292969</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5855,7 +5855,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D336">
-        <v>2.33013916015625</v>
+        <v>2.216291666030884</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5869,7 +5869,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D337">
-        <v>4.74429988861084</v>
+        <v>4.735721111297607</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5883,7 +5883,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D338">
-        <v>5.64903736114502</v>
+        <v>5.086068153381348</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5897,7 +5897,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D339">
-        <v>10.16401386260986</v>
+        <v>9.707563400268555</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5911,7 +5911,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D340">
-        <v>2.036075115203857</v>
+        <v>1.951987504959106</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5925,7 +5925,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D341">
-        <v>3.980027198791504</v>
+        <v>4.151341915130615</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5939,7 +5939,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D342">
-        <v>3.296622514724731</v>
+        <v>3.123455762863159</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5953,7 +5953,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D343">
-        <v>3.210415363311768</v>
+        <v>2.193643569946289</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5967,7 +5967,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D344">
-        <v>2.060947895050049</v>
+        <v>2.198365688323975</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5981,7 +5981,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D345">
-        <v>6.699737548828125</v>
+        <v>7.099880695343018</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5995,7 +5995,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D346">
-        <v>4.672933101654053</v>
+        <v>4.828818798065186</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6009,7 +6009,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D347">
-        <v>9.047677040100098</v>
+        <v>10.62311267852783</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6023,7 +6023,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D348">
-        <v>5.908733367919922</v>
+        <v>5.724560260772705</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6037,7 +6037,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>2.250155925750732</v>
+        <v>1.996042013168335</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6051,7 +6051,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D350">
-        <v>5.997793197631836</v>
+        <v>5.830543994903564</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6065,7 +6065,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D351">
-        <v>1.659233093261719</v>
+        <v>1.98692798614502</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6079,7 +6079,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D352">
-        <v>4.223385334014893</v>
+        <v>2.563068866729736</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6093,7 +6093,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>13.6411771774292</v>
+        <v>11.45968341827393</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6107,7 +6107,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D354">
-        <v>2.063461780548096</v>
+        <v>1.948754072189331</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6121,7 +6121,7 @@
         <v>15.5</v>
       </c>
       <c r="D355">
-        <v>7.092693328857422</v>
+        <v>7.510427474975586</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6135,7 +6135,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D356">
-        <v>1.720465183258057</v>
+        <v>1.794776201248169</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6149,7 +6149,7 @@
         <v>1.5</v>
       </c>
       <c r="D357">
-        <v>5.342769622802734</v>
+        <v>4.583609104156494</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6163,7 +6163,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D358">
-        <v>1.849353551864624</v>
+        <v>2.649487972259521</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6177,7 +6177,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D359">
-        <v>4.274345397949219</v>
+        <v>4.622026443481445</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6191,7 +6191,7 @@
         <v>5.5</v>
       </c>
       <c r="D360">
-        <v>1.78830623626709</v>
+        <v>1.970978975296021</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6205,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>1.915709733963013</v>
+        <v>2.159244775772095</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6219,7 +6219,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D362">
-        <v>6.209682464599609</v>
+        <v>6.040119647979736</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6233,7 +6233,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D363">
-        <v>9.66018009185791</v>
+        <v>9.310124397277832</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6247,7 +6247,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D364">
-        <v>2.037675619125366</v>
+        <v>2.078817129135132</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6261,7 +6261,7 @@
         <v>1.5</v>
       </c>
       <c r="D365">
-        <v>1.531451463699341</v>
+        <v>1.75398862361908</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6275,7 +6275,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D366">
-        <v>1.739119529724121</v>
+        <v>1.822932004928589</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6289,7 +6289,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D367">
-        <v>3.297959327697754</v>
+        <v>3.522871255874634</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6303,7 +6303,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D368">
-        <v>9.517949104309082</v>
+        <v>9.012881278991699</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6317,7 +6317,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D369">
-        <v>2.025788307189941</v>
+        <v>1.914099454879761</v>
       </c>
     </row>
   </sheetData>
